--- a/分析结果.xlsx
+++ b/分析结果.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色套装部位优化概率" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="套装优化概率" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地点优化概率" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="套装部位优化概率" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="套装优化准确概率" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10753,4 +10755,5087 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E185"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>套装名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>部位名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>该套装使用角色列表</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>套装部位提升概率</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>期望出货次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>流星追迹的怪盗</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>阮梅、</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>沉欢醉饮的海隅</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>黑天鹅、卡夫卡、</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.741455661142241e-06</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>重循苦旅的司铎</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>赛飞儿、</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.147583473598084e-05</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>骇域漫游的信使</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>赛飞儿、</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.147583473598084e-05</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>风举云飞的勇烈</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>飞霄、</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.147583473598084e-05</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>宝命长存的莳者</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>刃、</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.147583473598084e-05</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>奇想蕉乐园</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>景元、</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.907814366577246e-05</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>盗贼公国塔利亚</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>阮梅、</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.464738660435061e-05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>密林卧雪的猎人</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>彦青、</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4.465598370847129e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>妖精织梦的乐园</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>白厄、</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5.370284041536626e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>出云显世与高天神国</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>大黑塔、</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8.903184544645134e-05</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>奔狼的都蓝王朝</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>飞霄、</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8.903184544645134e-05</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>自匿星芒的隐士</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>盾丹、</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>9.383193797206044e-05</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>自匿星芒的隐士</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>盾丹、</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0001110677922663189</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>野穗伴行的快枪手</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>龙丹、</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0001188828544663974</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>荡除虫灾的铁骑</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>忘归人、</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.0001238755018487515</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>盗贼公国塔利亚</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>阮梅、</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0001248835586317759</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>劫火莲灯铸炼宫</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>忘归人、</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0001248835586317759</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>再创天地的救世主</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>记忆主、</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0002553894387073948</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>荡除虫灾的铁骑</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>流萤、</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0002581146856800012</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>幽锁深牢的系囚</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>卡夫卡、</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.0002581146856800012</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>闪耀功勋的魔法少女</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>银狼999、</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0004172115243003981</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7179</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>苍穹战线格拉默</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>希儿、</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0004362183492411145</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6867</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>繁星璀璨的天才</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>红A、</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0005678861967735525</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5274</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>恶海逐波的船长</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>saber、</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0005678861967735525</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5274</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>应天涉远的卜者</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>欢愉主、</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0005678861967735525</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5274</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>谧宁拾骨地</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>刃、</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0006086589072528484</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4921</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>自匿星芒的隐士</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>盾丹、</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0006312827503262552</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4744</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>停转的萨尔索图</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>托帕、姬子、</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0006607563256131343</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4533</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>闪耀功勋的魔法少女</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>银狼999、</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0007127115014380845</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4202</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>闪耀功勋的魔法少女</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>银狼999、</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0008283675450837723</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>识海迷坠的学者</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>镜流、</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0008809542030232964</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>密林卧雪的猎人</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>彦青、</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0008809542030232964</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>恶海逐波的船长</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>saber、</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0008809542030232964</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>烈阳惊雷的女武神</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>风堇、</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0009324514981223079</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3212</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>零号关卡朋克洛德</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>银狼999、</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.001038750275968222</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>沉欢醉饮的海隅</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>卡夫卡、</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.001085860792647293</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>沉欢醉饮的海隅</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>黑天鹅、</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.001085860792647294</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>生命的翁瓦克</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>椒丘、</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.001085860792647294</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>荡除虫灾的铁骑</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>忘归人、流萤、大丽花、</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.001093688083972288</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>妖精织梦的乐园</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>白厄、</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.001143249413509792</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>识海迷坠的学者</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>大黑塔、</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.001228724474857787</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>风举云飞的勇烈</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>云璃、</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.001228724474857787</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>繁星璀璨的天才</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>红A、</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.001228724474857787</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>沉陆海域的露莎卡</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>星期日、</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.0012935317590554</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>流星追迹的怪盗</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>阮梅、</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.001302186471993131</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>哀歌覆国的诗人</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>提宝、遐蝶、</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.00132620705910421</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>流星追迹的怪盗</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>阮梅、</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.001424371540448531</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>自匿星芒的隐士</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>盾丹、</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.001580173843121943</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>风举云飞的勇烈</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>云璃、</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.001832480575623524</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>再创天地的救世主</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>记忆主、</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.00193684574749315</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>出云显世与高天神国</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>黄泉、</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.002069346370087798</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>停转的萨尔索图</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>真理、</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.002069346370087798</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>哀歌覆国的诗人</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>提宝、遐蝶、克拉拉、</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.002241153082243384</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>繁星璀璨的天才</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>希儿、</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.002709909824021446</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>应天涉远的卜者</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>欢愉主、</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.002709909824021446</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>不老者的仙舟</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>白露、</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.003055998238351729</v>
+      </c>
+      <c r="E58" t="n">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>烈阳惊雷的女武神</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>风堇、</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.003203397601453594</v>
+      </c>
+      <c r="E59" t="n">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>荡除虫灾的铁骑</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>忘归人、流萤、大丽花、</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.003319636718004179</v>
+      </c>
+      <c r="E60" t="n">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>野穗伴行的快枪手</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>老杨、</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.003613827741980973</v>
+      </c>
+      <c r="E61" t="n">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>幽锁深牢的系囚</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>海瑟音、黑天鹅、卡夫卡、</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.003962518046398149</v>
+      </c>
+      <c r="E62" t="n">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>街头出身的拳王</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>银枝、</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.004109124577117677</v>
+      </c>
+      <c r="E63" t="n">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>净庭教宗的圣骑士</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>砂金、</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.004161718247407575</v>
+      </c>
+      <c r="E64" t="n">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>繁星璀璨的天才</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>希儿、</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.004161718247407581</v>
+      </c>
+      <c r="E65" t="n">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>渊思寂虑的巨树</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>风堇、</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.00420292824242234</v>
+      </c>
+      <c r="E66" t="n">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>不老者的仙舟</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>花火、</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.004202928242422342</v>
+      </c>
+      <c r="E67" t="n">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>闪耀功勋的魔法少女</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>银狼999、</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.004212288223715417</v>
+      </c>
+      <c r="E68" t="n">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>风举云飞的勇烈</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>云璃、飞霄、</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.004212288223715418</v>
+      </c>
+      <c r="E69" t="n">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>风举云飞的勇烈</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>云璃、飞霄、</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.004212288223715418</v>
+      </c>
+      <c r="E70" t="n">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>重循苦旅的司铎</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>星期日、</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.004478692931919767</v>
+      </c>
+      <c r="E71" t="n">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>骇域漫游的信使</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>布洛尼亚、花火、</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.004478692931919772</v>
+      </c>
+      <c r="E72" t="n">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>云无留迹的过客</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>霍霍、罗刹、白露、</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.004625395332650177</v>
+      </c>
+      <c r="E73" t="n">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>街头出身的拳王</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>银枝、</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.004677096133999823</v>
+      </c>
+      <c r="E74" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>密林卧雪的猎人</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>彦青、</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.004677096133999823</v>
+      </c>
+      <c r="E75" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>应天涉远的卜者</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>欢愉主、</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.004677096133999823</v>
+      </c>
+      <c r="E76" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>识海迷坠的学者</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>大黑塔、镜流、</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.004866350065908757</v>
+      </c>
+      <c r="E77" t="n">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>生命的翁瓦克</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>椒丘、</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.005192625162311227</v>
+      </c>
+      <c r="E78" t="n">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>恶海逐波的船长</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>白厄、</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.005459849672855587</v>
+      </c>
+      <c r="E79" t="n">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>停转的萨尔索图</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>银枝、</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.005467287872601218</v>
+      </c>
+      <c r="E80" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>谧宁拾骨地</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>镜流、</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.005467287872601218</v>
+      </c>
+      <c r="E81" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>繁星竞技场</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>红A、</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.005467287872601218</v>
+      </c>
+      <c r="E82" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>停转的萨尔索图</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>saber、</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.005467287872601218</v>
+      </c>
+      <c r="E83" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>泛银河商业公司</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>老杨、</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.005467287872601218</v>
+      </c>
+      <c r="E84" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>烈阳惊雷的女武神</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>风堇、</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.005812704780207856</v>
+      </c>
+      <c r="E85" t="n">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>恶海逐波的船长</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>白厄、</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.006017227451063314</v>
+      </c>
+      <c r="E86" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>再创天地的救世主</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>记忆主、</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.006245745696469984</v>
+      </c>
+      <c r="E87" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>烈阳惊雷的女武神</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>风堇、</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.006803602368889316</v>
+      </c>
+      <c r="E88" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>骇域漫游的信使</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>知更鸟、布洛尼亚、花火、赛飞儿、</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.007054289892157128</v>
+      </c>
+      <c r="E89" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>谧宁拾骨地</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>提宝、镜流、</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.007340428780352804</v>
+      </c>
+      <c r="E90" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>折断的龙骨</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>砂金、</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.007418117937299156</v>
+      </c>
+      <c r="E91" t="n">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>奇想蕉乐园</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>景元、</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.007418117937299171</v>
+      </c>
+      <c r="E92" t="n">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>重循苦旅的司铎</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>刻律德拉、</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.00793942203796077</v>
+      </c>
+      <c r="E93" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>密林卧雪的猎人</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>彦青、</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.008176451594023399</v>
+      </c>
+      <c r="E94" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>毁烬焚骨的大公</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>托帕、景元、姬子、</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.008202521890475989</v>
+      </c>
+      <c r="E95" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>戍卫风雪的铁卫</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>符玄、</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.008565024464550933</v>
+      </c>
+      <c r="E96" t="n">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>净庭教宗的圣骑士</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>杰帕德、</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.009105359202548841</v>
+      </c>
+      <c r="E97" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>奔狼的都蓝王朝</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>克拉拉、云璃、飞霄、</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.009262634273336465</v>
+      </c>
+      <c r="E98" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>荡除虫灾的铁骑</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>大丽花、</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.009364023097894322</v>
+      </c>
+      <c r="E99" t="n">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>毁烬焚骨的大公</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>托帕、景元、姬子、</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.009411780409890682</v>
+      </c>
+      <c r="E100" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>泛银河商业公司</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>银狼、</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.00969374439789265</v>
+      </c>
+      <c r="E101" t="n">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>重循苦旅的司铎</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>星期日、刻律德拉、赛飞儿、</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.009731929740899843</v>
+      </c>
+      <c r="E102" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>沉陆海域的露莎卡</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>赛飞儿、盾丹、</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.009880028417380053</v>
+      </c>
+      <c r="E103" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>沉欢醉饮的海隅</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>海瑟音、</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.01004204382047012</v>
+      </c>
+      <c r="E104" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>戍卫风雪的铁卫</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>符玄、</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.01030693414096571</v>
+      </c>
+      <c r="E105" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>宝命长存的莳者</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>符玄、</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.01030693414096571</v>
+      </c>
+      <c r="E106" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>幽锁深牢的系囚</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>海瑟音、黑天鹅、</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.01063496510120679</v>
+      </c>
+      <c r="E107" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>哀歌覆国的诗人</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>提宝、遐蝶、克拉拉、</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.01085507280581739</v>
+      </c>
+      <c r="E108" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>沉陆海域的露莎卡</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>赛飞儿、</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.01096963972421254</v>
+      </c>
+      <c r="E109" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>苍穹战线格拉默</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>希儿、</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0.01096963972421254</v>
+      </c>
+      <c r="E110" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>风举云飞的勇烈</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>飞霄、</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0.01114966604070134</v>
+      </c>
+      <c r="E111" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>不老者的仙舟</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>罗刹、</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.0115458404797037</v>
+      </c>
+      <c r="E112" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>劫火莲灯铸炼宫</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>流萤、</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.0115458404797037</v>
+      </c>
+      <c r="E113" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>毁烬焚骨的大公</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>托帕、景元、姬子、</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.01157964704236576</v>
+      </c>
+      <c r="E114" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>奔狼的都蓝王朝</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>克拉拉、云璃、</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0.01205127340594954</v>
+      </c>
+      <c r="E115" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>晨昏交界的翔鹰</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>银狼、椒丘、</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0.01230700253774672</v>
+      </c>
+      <c r="E116" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>重循苦旅的司铎</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>星期日、刻律德拉、赛飞儿、</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0.01233556700932678</v>
+      </c>
+      <c r="E117" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>折断的龙骨</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>杰帕德、砂金、</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.01325738721138294</v>
+      </c>
+      <c r="E118" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>净庭教宗的圣骑士</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>杰帕德、</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0.01328016639691748</v>
+      </c>
+      <c r="E119" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>沉陆海域的露莎卡</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>记忆主、</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0.0135888077148131</v>
+      </c>
+      <c r="E120" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>街头出身的拳王</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>银枝、</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0.01408577637812858</v>
+      </c>
+      <c r="E121" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>识海迷坠的学者</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>大黑塔、镜流、</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0.01419266187078552</v>
+      </c>
+      <c r="E122" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>街头出身的拳王</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>银枝、</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0.0149477325902308</v>
+      </c>
+      <c r="E123" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>应天涉远的卜者</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>欢愉主、</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0.0149477325902308</v>
+      </c>
+      <c r="E124" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>野穗伴行的快枪手</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>老杨、知更鸟、龙丹、</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0.01503828128109277</v>
+      </c>
+      <c r="E125" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>沉欢醉饮的海隅</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>海瑟音、</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0.01506306573070518</v>
+      </c>
+      <c r="E126" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>恶海逐波的船长</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>白厄、saber、</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0.01531375982460958</v>
+      </c>
+      <c r="E127" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>净庭教宗的圣骑士</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>杰帕德、砂金、</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0.01551118874002917</v>
+      </c>
+      <c r="E128" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>繁星璀璨的天才</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>希儿、红A、</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0.01592386128030542</v>
+      </c>
+      <c r="E129" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>重循苦旅的司铎</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>星期日、刻律德拉、赛飞儿、</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0.0166093969689428</v>
+      </c>
+      <c r="E130" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>不老者的仙舟</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>花火、符玄、</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0.01739559618761356</v>
+      </c>
+      <c r="E131" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>繁星竞技场</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>龙丹、红A、</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0.01755733353497925</v>
+      </c>
+      <c r="E132" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>零号关卡朋克洛德</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>银狼999、</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0.01755733353497928</v>
+      </c>
+      <c r="E133" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>晨昏交界的翔鹰</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>银狼、椒丘、</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0.01797649275862989</v>
+      </c>
+      <c r="E134" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>繁星璀璨的天才</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>希儿、红A、</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0.01807705086634119</v>
+      </c>
+      <c r="E135" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>净庭教宗的圣骑士</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>砂金、</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0.01857740718062601</v>
+      </c>
+      <c r="E136" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>骇域漫游的信使</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>布洛尼亚、花火、赛飞儿、</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0.01878606782747992</v>
+      </c>
+      <c r="E137" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>繁星竞技场</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>龙丹、</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0.01884714428922947</v>
+      </c>
+      <c r="E138" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>停转的萨尔索图</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>彦青、</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0.01884714428922947</v>
+      </c>
+      <c r="E139" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>野穗伴行的快枪手</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>知更鸟、</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0.01896457291930454</v>
+      </c>
+      <c r="E140" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>骇域漫游的信使</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>知更鸟、</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0.01896457291930454</v>
+      </c>
+      <c r="E141" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>死水深潜的先驱</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>衣服</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>黄泉、真理、</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0.0194089714485427</v>
+      </c>
+      <c r="E142" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>再创天地的救世主</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>记忆主、</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0.0198456762557745</v>
+      </c>
+      <c r="E143" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>流星追迹的怪盗</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>阮梅、</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0.02050082147740523</v>
+      </c>
+      <c r="E144" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>渊思寂虑的巨树</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>风堇、</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0.02051938506871546</v>
+      </c>
+      <c r="E145" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>沉陆海域的露莎卡</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>欢愉主、刻律德拉、星期日、记忆主、知更鸟、</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0.02103786667321282</v>
+      </c>
+      <c r="E146" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>折断的龙骨</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>霍霍、布洛尼亚、杰帕德、</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0.02105158254594509</v>
+      </c>
+      <c r="E147" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>戍卫风雪的铁卫</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>符玄、</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0.02178282153600094</v>
+      </c>
+      <c r="E148" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>宝命长存的莳者</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>刃、符玄、</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0.02181978318712458</v>
+      </c>
+      <c r="E149" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>哀歌覆国的诗人</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>提宝、遐蝶、克拉拉、</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0.02312356067538492</v>
+      </c>
+      <c r="E150" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>泛银河商业公司</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>银狼、</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.02340773071656774</v>
+      </c>
+      <c r="E151" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>荡除虫灾的铁骑</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>忘归人、流萤、大丽花、</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0.02360922556014614</v>
+      </c>
+      <c r="E152" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>幽锁深牢的系囚</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>海瑟音、黑天鹅、卡夫卡、</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.02376915873725213</v>
+      </c>
+      <c r="E153" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>谧宁拾骨地</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>提宝、遐蝶、</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0.02396768918134106</v>
+      </c>
+      <c r="E154" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>死水深潜的先驱</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>黄泉、真理、</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0.02434037163906523</v>
+      </c>
+      <c r="E155" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>不老者的仙舟</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>罗刹、</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0.02465547281675574</v>
+      </c>
+      <c r="E156" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>折断的龙骨</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>霍霍、布洛尼亚、</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0.02620600215107456</v>
+      </c>
+      <c r="E157" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>晨昏交界的翔鹰</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>银狼、椒丘、</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0.0263281556768685</v>
+      </c>
+      <c r="E158" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>宝命长存的莳者</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>刃、符玄、</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0.02638327535849234</v>
+      </c>
+      <c r="E159" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>骇域漫游的信使</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>知更鸟、</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0.02765982960280567</v>
+      </c>
+      <c r="E160" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>不老者的仙舟</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>白露、符玄、</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0.02860890274934176</v>
+      </c>
+      <c r="E161" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>晨昏交界的翔鹰</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>银狼、椒丘、</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0.03425158281933596</v>
+      </c>
+      <c r="E162" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>劫火莲灯铸炼宫</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>流萤、大丽花、</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0.03548481629516537</v>
+      </c>
+      <c r="E163" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>哀歌覆国的诗人</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>克拉拉、</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.03632880368784443</v>
+      </c>
+      <c r="E164" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>劫火莲灯铸炼宫</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>忘归人、大丽花、</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0.0364118663994796</v>
+      </c>
+      <c r="E165" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>野穗伴行的快枪手</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>老杨、知更鸟、龙丹、</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0.03749268021909111</v>
+      </c>
+      <c r="E166" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>死水深潜的先驱</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>黄泉、真理、</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0.03757708798965493</v>
+      </c>
+      <c r="E167" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>恶海逐波的船长</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>白厄、saber、</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0.03793251814977475</v>
+      </c>
+      <c r="E168" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>识海迷坠的学者</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>大黑塔、镜流、</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0.03854261960547059</v>
+      </c>
+      <c r="E169" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>毁烬焚骨的大公</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>托帕、景元、姬子、</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0.03854261960547067</v>
+      </c>
+      <c r="E170" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>云无留迹的过客</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>霍霍、罗刹、白露、</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0.03963487676228369</v>
+      </c>
+      <c r="E171" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>死水深潜的先驱</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>黄泉、真理、</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0.04127749578779872</v>
+      </c>
+      <c r="E172" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>骇域漫游的信使</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>知更鸟、布洛尼亚、花火、赛飞儿、</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>0.04375110590563447</v>
+      </c>
+      <c r="E173" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>云无留迹的过客</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>霍霍、罗刹、白露、</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0.04467663774515546</v>
+      </c>
+      <c r="E174" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>幽锁深牢的系囚</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>海瑟音、黑天鹅、卡夫卡、</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0.05153467070482856</v>
+      </c>
+      <c r="E175" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>宝命长存的莳者</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>刃、符玄、</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0.05161203543988847</v>
+      </c>
+      <c r="E176" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>戍卫风雪的铁卫</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>符玄、</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0.0543320545492665</v>
+      </c>
+      <c r="E177" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>野穗伴行的快枪手</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>老杨、知更鸟、龙丹、</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0.05500573418849497</v>
+      </c>
+      <c r="E178" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>沉陆海域的露莎卡</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>知更鸟、欢愉主、刻律德拉、盾丹、</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0.05840660567373675</v>
+      </c>
+      <c r="E179" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>出云显世与高天神国</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>大黑塔、黄泉、</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0.06558364080225872</v>
+      </c>
+      <c r="E180" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>泛银河商业公司</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>老杨、</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0.06558364080225876</v>
+      </c>
+      <c r="E181" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>谧宁拾骨地</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>刃、遐蝶、</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0.06563687117663895</v>
+      </c>
+      <c r="E182" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>云无留迹的过客</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>霍霍、罗刹、白露、</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>0.07647309287841746</v>
+      </c>
+      <c r="E183" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>停转的萨尔索图</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>绳子</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>姬子、saber、彦青、银枝、托帕、真理、</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0.09555067358990867</v>
+      </c>
+      <c r="E184" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>净庭教宗的圣骑士</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>头</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>杰帕德、砂金、</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>0.1524875956220249</v>
+      </c>
+      <c r="E185" t="n">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>套装名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>该套装使用角色列表</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>套装提升概率</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>期望出货次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>盗贼公国塔利亚</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>阮梅、</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0001595309452361265</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>妖精织梦的乐园</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>白厄、</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.001196952253925159</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>自匿星芒的隐士</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>盾丹、</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.002416356323686577</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>闪耀功勋的魔法少女</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>银狼999、</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.006170578794537671</v>
+      </c>
+      <c r="D5" t="n">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>生命的翁瓦克</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>椒丘、</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.006278485954958521</v>
+      </c>
+      <c r="D6" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>奇想蕉乐园</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>景元、</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.007437196080964943</v>
+      </c>
+      <c r="D7" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>苍穹战线格拉默</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>希儿、</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01140585807345365</v>
+      </c>
+      <c r="D8" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>密林卧雪的猎人</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>彦青、</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01377915791475499</v>
+      </c>
+      <c r="D9" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>烈阳惊雷的女武神</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>风堇、</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01675215624867307</v>
+      </c>
+      <c r="D10" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>零号关卡朋克洛德</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>银狼999、</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0185960838109475</v>
+      </c>
+      <c r="D11" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>奔狼的都蓝王朝</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>克拉拉、云璃、飞霄、</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.02140293952473245</v>
+      </c>
+      <c r="D12" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>风举云飞的勇烈</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>云璃、飞霄、</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.02264692337334947</v>
+      </c>
+      <c r="D13" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>应天涉远的卜者</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>欢愉主、</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.02290262474502562</v>
+      </c>
+      <c r="D14" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>流星追迹的怪盗</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>阮梅、</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0232273794898469</v>
+      </c>
+      <c r="D15" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>渊思寂虑的巨树</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>风堇、</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.02472231331113781</v>
+      </c>
+      <c r="D16" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>沉欢醉饮的海隅</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>海瑟音、黑天鹅、卡夫卡、</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.02728657259213103</v>
+      </c>
+      <c r="D17" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>再创天地的救世主</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>记忆主、</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.02828365713844503</v>
+      </c>
+      <c r="D18" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>荡除虫灾的铁骑</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>忘归人、流萤、大丽花、</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.03776856364754568</v>
+      </c>
+      <c r="D19" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>街头出身的拳王</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>银枝、</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.03781972967947687</v>
+      </c>
+      <c r="D20" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>繁星竞技场</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>龙丹、红A、</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.04187176569680993</v>
+      </c>
+      <c r="D21" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>繁星璀璨的天才</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>希儿、红A、</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.04266915088970697</v>
+      </c>
+      <c r="D22" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>重循苦旅的司铎</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>刻律德拉、星期日、赛飞儿、</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.05110648452378594</v>
+      </c>
+      <c r="D23" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>识海迷坠的学者</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>大黑塔、镜流、</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.05971131022004596</v>
+      </c>
+      <c r="D24" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>恶海逐波的船长</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>白厄、saber、</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.06617219549810008</v>
+      </c>
+      <c r="D25" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>毁烬焚骨的大公</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>姬子、托帕、景元、</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0677365689482031</v>
+      </c>
+      <c r="D26" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>出云显世与高天神国</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>大黑塔、黄泉、</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.06774201901779296</v>
+      </c>
+      <c r="D27" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>折断的龙骨</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>杰帕德、砂金、霍霍、布洛尼亚、</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.06793308984570175</v>
+      </c>
+      <c r="D28" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>哀歌覆国的诗人</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>提宝、遐蝶、克拉拉、</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.07387479731039434</v>
+      </c>
+      <c r="D29" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>劫火莲灯铸炼宫</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>忘归人、流萤、大丽花、</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.08356740673298044</v>
+      </c>
+      <c r="D30" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>不老者的仙舟</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>白露、罗刹、花火、符玄、</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.08946473871418884</v>
+      </c>
+      <c r="D31" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>幽锁深牢的系囚</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>海瑟音、黑天鹅、卡夫卡、</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.09015942727536563</v>
+      </c>
+      <c r="D32" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>晨昏交界的翔鹰</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>银狼、椒丘、</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.09086323379258107</v>
+      </c>
+      <c r="D33" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>戍卫风雪的铁卫</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>符玄、</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.09498683469078409</v>
+      </c>
+      <c r="D34" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>谧宁拾骨地</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>提宝、镜流、遐蝶、刃、</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1030209359181869</v>
+      </c>
+      <c r="D35" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>泛银河商业公司</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>老杨、银狼、</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1041524037893204</v>
+      </c>
+      <c r="D36" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>宝命长存的莳者</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>刃、符玄、</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1101335039612071</v>
+      </c>
+      <c r="D37" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>沉陆海域的露莎卡</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>欢愉主、刻律德拉、星期日、记忆主、知更鸟、盾丹、赛飞儿、</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.1151764799624107</v>
+      </c>
+      <c r="D38" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>骇域漫游的信使</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>知更鸟、布洛尼亚、花火、赛飞儿、</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1207060349140375</v>
+      </c>
+      <c r="D39" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>死水深潜的先驱</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>黄泉、真理、</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.1226039268650616</v>
+      </c>
+      <c r="D40" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>停转的萨尔索图</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>姬子、saber、彦青、银枝、托帕、真理、</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1280624963200415</v>
+      </c>
+      <c r="D41" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>野穗伴行的快枪手</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>知更鸟、老杨、龙丹、</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.1302339792044307</v>
+      </c>
+      <c r="D42" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>云无留迹的过客</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>白露、罗刹、霍霍、</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.1654100027185068</v>
+      </c>
+      <c r="D43" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>净庭教宗的圣骑士</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>杰帕德、砂金、</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.213123435389554</v>
+      </c>
+      <c r="D44" t="n">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/分析结果.xlsx
+++ b/分析结果.xlsx
@@ -11,8 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色套装部位优化概率" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="套装部位优化概率" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="套装优化准确概率" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(旧)套装优化概率" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(旧)地点优化概率" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地点优化概率" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(旧)套装优化概率" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(旧)地点优化概率" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +452,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>期望出货次数</t>
+          <t>95%期望出货次数</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2244,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>期望出货次数</t>
+          <t>95%期望出货次数</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9341,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>期望出货次数</t>
+          <t>95%期望出货次数</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10002,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>托帕、姬子、</t>
+          <t>姬子、托帕、</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -10415,7 +10416,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>遐蝶、提宝、</t>
+          <t>提宝、遐蝶、</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -10576,7 +10577,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>遐蝶、克拉拉、提宝、</t>
+          <t>克拉拉、提宝、遐蝶、</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -10737,7 +10738,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>海瑟音、黑天鹅、卡夫卡、</t>
+          <t>海瑟音、卡夫卡、黑天鹅、</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -10898,7 +10899,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>飞霄、云璃、</t>
+          <t>云璃、飞霄、</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -10921,7 +10922,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>飞霄、云璃、</t>
+          <t>云璃、飞霄、</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -10990,7 +10991,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>霍霍、白露、罗刹、</t>
+          <t>罗刹、霍霍、白露、</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -11358,7 +11359,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>布洛尼亚、花火、赛飞儿、知更鸟、</t>
+          <t>知更鸟、布洛尼亚、花火、赛飞儿、</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -11496,7 +11497,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>托帕、姬子、景元、</t>
+          <t>姬子、托帕、景元、</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -11565,7 +11566,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>飞霄、克拉拉、云璃、</t>
+          <t>克拉拉、云璃、飞霄、</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -11611,7 +11612,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>托帕、姬子、景元、</t>
+          <t>姬子、托帕、景元、</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -11657,7 +11658,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>刻律德拉、星期日、赛飞儿、</t>
+          <t>刻律德拉、赛飞儿、星期日、</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -11795,7 +11796,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>遐蝶、克拉拉、提宝、</t>
+          <t>克拉拉、提宝、遐蝶、</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -11933,7 +11934,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>托帕、姬子、景元、</t>
+          <t>姬子、托帕、景元、</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -11979,7 +11980,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>椒丘、银狼、</t>
+          <t>银狼、椒丘、</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -12002,7 +12003,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>刻律德拉、星期日、赛飞儿、</t>
+          <t>刻律德拉、赛飞儿、星期日、</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -12025,7 +12026,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>砂金、杰帕德、</t>
+          <t>杰帕德、砂金、</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -12186,7 +12187,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>龙丹、老杨、知更鸟、</t>
+          <t>知更鸟、龙丹、老杨、</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -12232,7 +12233,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>saber、白厄、</t>
+          <t>白厄、saber、</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -12255,7 +12256,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>砂金、杰帕德、</t>
+          <t>杰帕德、砂金、</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -12278,7 +12279,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>红A、希儿、</t>
+          <t>希儿、红A、</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -12301,7 +12302,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>刻律德拉、星期日、赛飞儿、</t>
+          <t>刻律德拉、赛飞儿、星期日、</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -12324,7 +12325,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>花火、符玄、</t>
+          <t>符玄、花火、</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -12347,7 +12348,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>龙丹、红A、</t>
+          <t>红A、龙丹、</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -12393,7 +12394,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>椒丘、银狼、</t>
+          <t>银狼、椒丘、</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -12416,7 +12417,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>红A、希儿、</t>
+          <t>希儿、红A、</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -12669,7 +12670,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>欢愉主、知更鸟、记忆主、刻律德拉、星期日、</t>
+          <t>星期日、知更鸟、刻律德拉、欢愉主、记忆主、</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -12692,7 +12693,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>霍霍、布洛尼亚、杰帕德、</t>
+          <t>杰帕德、布洛尼亚、霍霍、</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -12738,7 +12739,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>刃、符玄、</t>
+          <t>符玄、刃、</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -12761,7 +12762,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>遐蝶、克拉拉、提宝、</t>
+          <t>克拉拉、提宝、遐蝶、</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -12830,7 +12831,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>海瑟音、黑天鹅、卡夫卡、</t>
+          <t>海瑟音、卡夫卡、黑天鹅、</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -12853,7 +12854,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>遐蝶、提宝、</t>
+          <t>提宝、遐蝶、</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -12922,7 +12923,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>霍霍、布洛尼亚、</t>
+          <t>布洛尼亚、霍霍、</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -12945,7 +12946,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>椒丘、银狼、</t>
+          <t>银狼、椒丘、</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -12968,7 +12969,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>刃、符玄、</t>
+          <t>符玄、刃、</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -13014,7 +13015,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>白露、符玄、</t>
+          <t>符玄、白露、</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -13037,7 +13038,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>椒丘、银狼、</t>
+          <t>银狼、椒丘、</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -13129,7 +13130,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>龙丹、老杨、知更鸟、</t>
+          <t>知更鸟、龙丹、老杨、</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -13175,7 +13176,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>saber、白厄、</t>
+          <t>白厄、saber、</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -13221,7 +13222,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>托帕、姬子、景元、</t>
+          <t>姬子、托帕、景元、</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -13244,7 +13245,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>霍霍、白露、罗刹、</t>
+          <t>罗刹、霍霍、白露、</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -13290,7 +13291,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>布洛尼亚、花火、赛飞儿、知更鸟、</t>
+          <t>知更鸟、布洛尼亚、花火、赛飞儿、</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -13313,7 +13314,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>霍霍、白露、罗刹、</t>
+          <t>罗刹、霍霍、白露、</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -13336,7 +13337,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>海瑟音、黑天鹅、卡夫卡、</t>
+          <t>海瑟音、卡夫卡、黑天鹅、</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -13359,7 +13360,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>刃、符玄、</t>
+          <t>符玄、刃、</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -13405,7 +13406,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>龙丹、老杨、知更鸟、</t>
+          <t>知更鸟、龙丹、老杨、</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -13428,7 +13429,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>刻律德拉、盾丹、欢愉主、知更鸟、</t>
+          <t>知更鸟、盾丹、刻律德拉、欢愉主、</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -13451,7 +13452,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>黄泉、大黑塔、</t>
+          <t>大黑塔、黄泉、</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -13497,7 +13498,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>遐蝶、刃、</t>
+          <t>刃、遐蝶、</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -13520,7 +13521,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>霍霍、白露、罗刹、</t>
+          <t>罗刹、霍霍、白露、</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -13543,7 +13544,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>彦青、银枝、saber、托帕、姬子、真理、</t>
+          <t>saber、银枝、真理、姬子、托帕、彦青、</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -13566,7 +13567,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>砂金、杰帕德、</t>
+          <t>杰帕德、砂金、</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -13608,7 +13609,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>期望出货次数</t>
+          <t>95%期望出货次数</t>
         </is>
       </c>
     </row>
@@ -13800,7 +13801,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>飞霄、克拉拉、云璃、</t>
+          <t>克拉拉、云璃、飞霄、</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -13818,7 +13819,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>飞霄、云璃、</t>
+          <t>云璃、飞霄、</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -13890,7 +13891,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>卡夫卡、黑天鹅、海瑟音、</t>
+          <t>海瑟音、卡夫卡、黑天鹅、</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -13926,7 +13927,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>忘归人、流萤、大丽花、</t>
+          <t>忘归人、大丽花、流萤、</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -13962,7 +13963,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>龙丹、红A、</t>
+          <t>红A、龙丹、</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -13980,7 +13981,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>希儿、红A、</t>
+          <t>红A、希儿、</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -13998,7 +13999,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>刻律德拉、星期日、赛飞儿、</t>
+          <t>刻律德拉、赛飞儿、星期日、</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -14034,7 +14035,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>saber、白厄、</t>
+          <t>白厄、saber、</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -14052,7 +14053,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>姬子、托帕、景元、</t>
+          <t>景元、姬子、托帕、</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -14070,7 +14071,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>黄泉、大黑塔、</t>
+          <t>大黑塔、黄泉、</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -14088,7 +14089,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>布洛尼亚、砂金、霍霍、杰帕德、</t>
+          <t>砂金、杰帕德、布洛尼亚、霍霍、</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -14106,7 +14107,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>遐蝶、克拉拉、提宝、</t>
+          <t>克拉拉、提宝、遐蝶、</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -14124,7 +14125,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>忘归人、流萤、大丽花、</t>
+          <t>忘归人、大丽花、流萤、</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -14142,7 +14143,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>白露、罗刹、符玄、花火、</t>
+          <t>罗刹、符玄、花火、白露、</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -14160,7 +14161,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>海瑟音、黑天鹅、卡夫卡、</t>
+          <t>海瑟音、卡夫卡、黑天鹅、</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -14178,7 +14179,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>椒丘、银狼、</t>
+          <t>银狼、椒丘、</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -14214,7 +14215,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>遐蝶、刃、提宝、镜流、</t>
+          <t>镜流、刃、遐蝶、提宝、</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -14250,7 +14251,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>刃、符玄、</t>
+          <t>符玄、刃、</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -14268,7 +14269,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>欢愉主、知更鸟、记忆主、刻律德拉、星期日、赛飞儿、盾丹、</t>
+          <t>赛飞儿、星期日、知更鸟、盾丹、刻律德拉、欢愉主、记忆主、</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -14286,7 +14287,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>布洛尼亚、花火、知更鸟、赛飞儿、</t>
+          <t>赛飞儿、知更鸟、花火、布洛尼亚、</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -14322,7 +14323,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>彦青、saber、银枝、托帕、姬子、真理、</t>
+          <t>saber、银枝、真理、姬子、托帕、彦青、</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -14358,7 +14359,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>白露、罗刹、霍霍、</t>
+          <t>罗刹、白露、霍霍、</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -14376,7 +14377,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>砂金、杰帕德、</t>
+          <t>杰帕德、砂金、</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -14397,803 +14398,632 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>套装名称</t>
+          <t>刷取地点</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>套装提升概率</t>
+          <t>地点提升概率</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>该套装使用角色列表</t>
+          <t>可刷取套装列表</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>期望出货次数</t>
+          <t>该地点可提升角色列表</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>95%期望出货次数</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>盗贼公国塔利亚</t>
+          <t>浴火钢心</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001595309452361265</v>
+        <v>0.006438016900194648</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>阮梅、</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>10000</v>
+          <t>盗贼公国塔利亚、生命的翁瓦克、</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>阮梅、椒丘、</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>464</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>妖精织梦的乐园</t>
+          <t>天剑如雨</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001196952253925159</v>
+        <v>0.01140585807345365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>白厄、</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2502</v>
+          <t>苍穹战线格拉默、</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>希儿、</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>262</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>自匿星芒的隐士</t>
+          <t>鎏金追忆</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002416356323686577</v>
+        <v>0.0185960838109475</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>盾丹、</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1239</v>
+          <t>零号关卡朋克洛德、</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>银狼999、</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>闪耀功勋的魔法少女</t>
+          <t>月下朱殷</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006170578794537671</v>
+        <v>0.02848352484605619</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>银狼999、</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>484</v>
+          <t>妖精织梦的乐园、沉欢醉饮的海隅、</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>白厄、卡夫卡、海瑟音、黑天鹅、</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>生命的翁瓦克</t>
+          <t>魔占之径</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006278485954958521</v>
+        <v>0.02907320353956329</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>椒丘、</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>476</v>
+          <t>闪耀功勋的魔法少女、应天涉远的卜者、</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>欢愉主、银狼999、</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>奇想蕉乐园</t>
+          <t>隐救之径</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007437196080964943</v>
+        <v>0.0307000134621316</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>景元、</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>402</v>
+          <t>自匿星芒的隐士、再创天地的救世主、</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>盾丹、记忆主、</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>苍穹战线格拉默</t>
+          <t>勇骑之径</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01140585807345365</v>
+        <v>0.06041548702089515</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>希儿、</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>262</v>
+          <t>风举云飞的勇烈、荡除虫灾的铁骑、</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>云璃、飞霄、忘归人、大丽花、流萤、</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>密林卧雪的猎人</t>
+          <t>迅拳之径</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01377915791475499</v>
+        <v>0.06104710916932377</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>彦青、</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>216</v>
+          <t>流星追迹的怪盗、街头出身的拳王、</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>银枝、阮梅、</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>烈阳惊雷的女武神</t>
+          <t>伴你入眠</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01675215624867308</v>
+        <v>0.06774201901779296</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>风堇、</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>178</v>
+          <t>出云显世与高天神国、</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>大黑塔、黄泉、</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>零号关卡朋克洛德</t>
+          <t>弦歌之径</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0185960838109475</v>
+        <v>0.07387479731039434</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>银狼999、</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>160</v>
+          <t>哀歌覆国的诗人、</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>克拉拉、提宝、遐蝶、</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>奔狼的都蓝王朝</t>
+          <t>雳涌之径</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01931416222643029</v>
+        <v>0.08292435174677315</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>云璃、飞霄、克拉拉、</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>154</v>
+          <t>烈阳惊雷的女武神、恶海逐波的船长、</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>风堇、白厄、saber、</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>应天涉远的卜者</t>
+          <t>坚城不倒</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02290262474502562</v>
+        <v>0.08946473871418884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>欢愉主、</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>130</v>
+          <t>不老者的仙舟、</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>符玄、罗刹、花火、白露、</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>流星追迹的怪盗</t>
+          <t>温柔话语</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0232273794898469</v>
+        <v>0.1041524037893204</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>阮梅、</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>128</v>
+          <t>泛银河商业公司、</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>银狼、老杨、</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>渊思寂虑的巨树</t>
+          <t>霜风之径</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02472231331113781</v>
+        <v>0.1046423917073361</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>风堇、</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>120</v>
+          <t>密林卧雪的猎人、晨昏交界的翔鹰、</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>椒丘、彦青、银狼、</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>风举云飞的勇烈</t>
+          <t>永恒笑剧</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02501819819990687</v>
+        <v>0.1049703462577129</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>云璃、飞霄、</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>119</v>
+          <t>奔狼的都蓝王朝、劫火莲灯铸炼宫、</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>克拉拉、云璃、飞霄、忘归人、大丽花、流萤、</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>荡除虫灾的铁骑</t>
+          <t>孽果盘生</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02756134437084194</v>
+        <v>0.1098048555425117</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>大丽花、流萤、忘归人、</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>108</v>
+          <t>繁星竞技场、折断的龙骨、</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>红A、龙丹、砂金、杰帕德、布洛尼亚、霍霍、</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>再创天地的救世主</t>
+          <t>迷识之径</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02828365713844503</v>
+        <v>0.1108177947438319</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>记忆主、</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>105</v>
+          <t>重循苦旅的司铎、识海迷坠的学者、</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>大黑塔、刻律德拉、赛飞儿、星期日、镜流、</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>繁星璀璨的天才</t>
+          <t>梦潜之径</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.03369099310428511</v>
+        <v>0.1226039268650616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>希儿、红A、</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>88</v>
+          <t>死水深潜的先驱、</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>黄泉、真理、</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>识海迷坠的学者</t>
+          <t>虫役饥肠</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.03520059731061695</v>
+        <v>0.1226136760433756</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>大黑塔、镜流、</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>84</v>
+          <t>奇想蕉乐园、沉陆海域的露莎卡、</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>赛飞儿、景元、星期日、知更鸟、盾丹、刻律德拉、欢愉主、记忆主、</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>恶海逐波的船长</t>
+          <t>纷争不休</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.03644204956208612</v>
+        <v>0.1277432492293247</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>白厄、saber、</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>81</v>
+          <t>渊思寂虑的巨树、谧宁拾骨地、</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>风堇、镜流、刃、遐蝶、提宝、</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>街头出身的拳王</t>
+          <t>百年冻土</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.03781972967947688</v>
+        <v>0.1280624963200415</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>银枝、</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>78</v>
+          <t>停转的萨尔索图、</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>银枝、saber、真理、姬子、托帕、彦青、</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>繁星竞技场</t>
+          <t>睿治之径</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.03915066803642903</v>
+        <v>0.1376559855804911</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>龙丹、红A、</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>76</v>
+          <t>繁星璀璨的天才、戍卫风雪的铁卫、</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>红A、符玄、希儿、</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>出云显世与高天神国</t>
+          <t>幽冥之径</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.04092591825492531</v>
+        <v>0.1578959962235687</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>大黑塔、黄泉、</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>72</v>
+          <t>毁烬焚骨的大公、幽锁深牢的系囚、</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>海瑟音、景元、姬子、托帕、卡夫卡、黑天鹅、</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>晨昏交界的翔鹰</t>
+          <t>圣颂之径</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04492640353846813</v>
+        <v>0.213123435389554</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>椒丘、银狼、</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>66</v>
+          <t>净庭教宗的圣骑士、</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>杰帕德、砂金、</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>毁烬焚骨的大公</t>
+          <t>药使之径</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.05153087071205589</v>
+        <v>0.2308395388752446</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>景元、托帕、姬子、</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>57</v>
+          <t>宝命长存的莳者、骇域漫游的信使、</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>符玄、赛飞儿、刃、花火、知更鸟、布洛尼亚、</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>沉欢醉饮的海隅</t>
+          <t>漂泊之径</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.05197998689383355</v>
+        <v>0.2956439819229375</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>海瑟音、黑天鹅、卡夫卡、</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>重循苦旅的司铎</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0.05238838493765449</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>刻律德拉、星期日、赛飞儿、</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>幽锁深牢的系囚</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0.05271102178427606</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>海瑟音、黑天鹅、卡夫卡、</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>劫火莲灯铸炼宫</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0.05700608814033464</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>大丽花、流萤、忘归人、</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>谧宁拾骨地</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0.0635635852873359</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>遐蝶、提宝、镜流、刃、</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>不老者的仙舟</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0.06614362332065619</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>花火、白露、罗刹、符玄、</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>折断的龙骨</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0.06695343562764083</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>霍霍、布洛尼亚、砂金、杰帕德、</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>哀歌覆国的诗人</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0.08332607438938051</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>遐蝶、提宝、克拉拉、</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>死水深潜的先驱</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0.08460988584573717</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>黄泉、真理、</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>沉陆海域的露莎卡</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0.09140964400128412</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>盾丹、记忆主、刻律德拉、星期日、赛飞儿、知更鸟、欢愉主、</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>戍卫风雪的铁卫</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0.0949868346907841</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>符玄、</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>云无留迹的过客</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0.1013379504412079</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>霍霍、白露、罗刹、</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>泛银河商业公司</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0.1041524037893204</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>老杨、银狼、</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>野穗伴行的快枪手</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0.1128094456105123</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>知更鸟、龙丹、老杨、</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>宝命长存的莳者</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0.1159270604148813</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>符玄、刃、</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>骇域漫游的信使</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0.1214546758427058</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>花火、布洛尼亚、赛飞儿、知更鸟、</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>净庭教宗的圣骑士</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.223170808753149</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>砂金、杰帕德、</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>停转的萨尔索图</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0.2485282997058577</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>真理、银枝、彦青、托帕、saber、姬子、</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11</v>
+          <t>野穗伴行的快枪手、云无留迹的过客、</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>龙丹、罗刹、老杨、知更鸟、白露、霍霍、</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -15207,6 +15037,816 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>套装名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>套装提升概率</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>该套装使用角色列表</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95%期望出货次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>盗贼公国塔利亚</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.0001595309452361265</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>阮梅、</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>妖精织梦的乐园</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.001196952253925159</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>白厄、</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>自匿星芒的隐士</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.002416356323686577</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>盾丹、</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>闪耀功勋的魔法少女</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.006170578794537671</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>银狼999、</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>生命的翁瓦克</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.006278485954958521</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>椒丘、</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>奇想蕉乐园</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.007437196080964943</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>景元、</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>苍穹战线格拉默</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.01140585807345365</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>希儿、</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>密林卧雪的猎人</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01377915791475499</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>彦青、</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>烈阳惊雷的女武神</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01675215624867308</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>风堇、</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>零号关卡朋克洛德</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0185960838109475</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>银狼999、</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>奔狼的都蓝王朝</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.01931416222643029</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>云璃、飞霄、克拉拉、</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>应天涉远的卜者</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.02290262474502562</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>欢愉主、</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>流星追迹的怪盗</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0232273794898469</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>阮梅、</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>渊思寂虑的巨树</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.02472231331113781</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>风堇、</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>风举云飞的勇烈</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.02501819819990687</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>云璃、飞霄、</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>荡除虫灾的铁骑</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.02756134437084194</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>大丽花、流萤、忘归人、</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>再创天地的救世主</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.02828365713844503</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>记忆主、</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>繁星璀璨的天才</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.03369099310428511</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>希儿、红A、</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>识海迷坠的学者</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.03520059731061695</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>大黑塔、镜流、</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>恶海逐波的船长</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.03644204956208612</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>白厄、saber、</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>街头出身的拳王</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.03781972967947688</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>银枝、</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>繁星竞技场</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.03915066803642903</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>龙丹、红A、</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>出云显世与高天神国</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.04092591825492531</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>大黑塔、黄泉、</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>晨昏交界的翔鹰</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.04492640353846813</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>椒丘、银狼、</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>毁烬焚骨的大公</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.05153087071205589</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>景元、托帕、姬子、</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>沉欢醉饮的海隅</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.05197998689383355</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>海瑟音、黑天鹅、卡夫卡、</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>重循苦旅的司铎</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.05238838493765449</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>刻律德拉、星期日、赛飞儿、</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>幽锁深牢的系囚</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.05271102178427606</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>海瑟音、黑天鹅、卡夫卡、</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>劫火莲灯铸炼宫</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.05700608814033464</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>大丽花、流萤、忘归人、</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>谧宁拾骨地</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.0635635852873359</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>遐蝶、提宝、镜流、刃、</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>不老者的仙舟</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.06614362332065619</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>花火、白露、罗刹、符玄、</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>折断的龙骨</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.06695343562764083</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>霍霍、布洛尼亚、砂金、杰帕德、</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>哀歌覆国的诗人</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.08332607438938051</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>遐蝶、提宝、克拉拉、</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>死水深潜的先驱</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.08460988584573717</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>黄泉、真理、</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>沉陆海域的露莎卡</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.09140964400128412</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>盾丹、记忆主、刻律德拉、星期日、赛飞儿、知更鸟、欢愉主、</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>戍卫风雪的铁卫</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.0949868346907841</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>符玄、</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>云无留迹的过客</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.1013379504412079</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>霍霍、白露、罗刹、</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>泛银河商业公司</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.1041524037893204</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>老杨、银狼、</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>野穗伴行的快枪手</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.1128094456105123</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>知更鸟、龙丹、老杨、</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>宝命长存的莳者</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.1159270604148813</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>符玄、刃、</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>骇域漫游的信使</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.1214546758427058</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>花火、布洛尼亚、赛飞儿、知更鸟、</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>净庭教宗的圣骑士</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.223170808753149</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>砂金、杰帕德、</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>停转的萨尔索图</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.2485282997058577</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>真理、银枝、彦青、托帕、saber、姬子、</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -15233,7 +15873,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>期望出货次数</t>
+          <t>95%期望出货次数</t>
         </is>
       </c>
     </row>
